--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,6 +124,12 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -201,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +273,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3652,7 +3661,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -3662,12 +3671,12 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3677,12 +3686,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3692,7 +3701,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3731,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3732,12 +3741,12 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3747,12 +3756,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3762,7 +3771,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3801,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3802,12 +3811,12 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -3817,12 +3826,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3832,7 +3841,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3941,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -3942,12 +3951,12 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -3957,12 +3966,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -3972,7 +3981,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4011,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -4012,12 +4021,12 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -4027,12 +4036,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -4042,7 +4051,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4081,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4082,12 +4091,12 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -4097,12 +4106,12 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -4112,7 +4121,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4221,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4222,12 +4231,12 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -4237,12 +4246,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4252,7 +4261,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4501,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4502,12 +4511,12 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -4517,12 +4526,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4532,7 +4541,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5311,27 +5320,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6093,12 @@
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr"/>
-      <c r="C34" s="21" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -6112,20 +6121,20 @@
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr"/>
-      <c r="C35" s="21" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr"/>
@@ -6140,12 +6149,12 @@
         </is>
       </c>
       <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="21" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -6168,20 +6177,20 @@
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr"/>
-      <c r="C37" s="21" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr"/>
@@ -6196,12 +6205,12 @@
         </is>
       </c>
       <c r="B38" s="20" t="inlineStr"/>
-      <c r="C38" s="21" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -6252,12 +6261,12 @@
         </is>
       </c>
       <c r="B40" s="20" t="inlineStr"/>
-      <c r="C40" s="21" t="inlineStr">
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4011,23 +4011,19 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>124313590</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>44830</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4036,12 +4032,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -4051,7 +4047,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4081,23 +4077,19 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>129396960</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>46680</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4106,12 +4098,12 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -4121,7 +4113,7 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4353,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -4371,12 +4363,12 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -4386,12 +4378,12 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -4401,7 +4393,7 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4633,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4651,12 +4643,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -4666,12 +4658,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4681,7 +4673,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5312,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5330,7 +5322,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5340,7 +5332,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6093,63 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
+      <c r="G34" s="20" t="inlineStr"/>
+      <c r="H34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr"/>
+      <c r="F35" s="20" t="inlineStr"/>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
 -
@@ -6109,19 +6157,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr"/>
-      <c r="F34" s="20" t="inlineStr"/>
-      <c r="G34" s="20" t="inlineStr"/>
-      <c r="H34" s="20" t="inlineStr"/>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr"/>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr"/>
+      <c r="F36" s="20" t="inlineStr"/>
+      <c r="G36" s="20" t="inlineStr"/>
+      <c r="H36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr"/>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12940万
+$46,680/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+$12431万
+$44,830/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr"/>
+      <c r="F37" s="20" t="inlineStr"/>
+      <c r="G37" s="20" t="inlineStr"/>
+      <c r="H37" s="20" t="inlineStr"/>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
 招标单位
@@ -6129,27 +6205,27 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
-招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr"/>
-      <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="20" t="inlineStr"/>
-      <c r="H35" s="20" t="inlineStr"/>
-    </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="23" t="inlineStr">
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr"/>
+      <c r="F38" s="20" t="inlineStr"/>
+      <c r="G38" s="20" t="inlineStr"/>
+      <c r="H38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
 招标单位
@@ -6157,7 +6233,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
 -
@@ -6165,19 +6241,19 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr"/>
-      <c r="F36" s="20" t="inlineStr"/>
-      <c r="G36" s="20" t="inlineStr"/>
-      <c r="H36" s="20" t="inlineStr"/>
-    </row>
-    <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr"/>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="20" t="inlineStr"/>
+      <c r="G39" s="20" t="inlineStr"/>
+      <c r="H39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
 招标单位
@@ -6185,116 +6261,32 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
-招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr"/>
-      <c r="F37" s="20" t="inlineStr"/>
-      <c r="G37" s="20" t="inlineStr"/>
-      <c r="H37" s="20" t="inlineStr"/>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr"/>
-      <c r="C38" s="23" t="inlineStr">
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr"/>
+      <c r="F40" s="20" t="inlineStr"/>
+      <c r="G40" s="20" t="inlineStr"/>
+      <c r="H40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
 招标单位
 -
 (在售)</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E38" s="20" t="inlineStr"/>
-      <c r="F38" s="20" t="inlineStr"/>
-      <c r="G38" s="20" t="inlineStr"/>
-      <c r="H38" s="20" t="inlineStr"/>
-    </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="21" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="20" t="inlineStr"/>
-      <c r="F39" s="20" t="inlineStr"/>
-      <c r="G39" s="20" t="inlineStr"/>
-      <c r="H39" s="20" t="inlineStr"/>
-    </row>
-    <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr"/>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E40" s="20" t="inlineStr"/>
-      <c r="F40" s="20" t="inlineStr"/>
-      <c r="G40" s="20" t="inlineStr"/>
-      <c r="H40" s="20" t="inlineStr"/>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="21" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5590</v>
+        <v>5483</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>408690000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>73111</v>
+        <v>74538</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -3661,23 +3661,19 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>134442000</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>48500</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3686,12 +3682,12 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -3701,7 +3697,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3731,23 +3727,19 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>130552000</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>47080</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3756,12 +3748,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3771,7 +3763,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3801,23 +3793,19 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>133056000</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>48000</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3826,12 +3814,12 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -3841,7 +3829,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3941,23 +3929,19 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>131115600</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>47300</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3966,12 +3950,12 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -3981,7 +3965,7 @@
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4213,23 +4197,19 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>127761000</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>46090</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4238,12 +4218,12 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4253,7 +4233,7 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4353,23 +4333,19 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>128371000</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>46310</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4378,12 +4354,12 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -4393,7 +4369,7 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4493,23 +4469,19 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>127512000</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>46000</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4518,12 +4490,12 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -4533,7 +4505,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4913,23 +4885,19 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>126957600</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>45800</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -5312,7 +5280,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5322,7 +5290,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5332,7 +5300,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -5680,9 +5648,9 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>- | 5590呎 (3房)
+          <t>- | 5483呎 (3房)
 $40869万
-$73,111/呎
+$74,538/呎
 (26年-08月-19日)</t>
         </is>
       </c>
@@ -6085,7 +6053,203 @@
         </is>
       </c>
       <c r="B34" s="20" t="inlineStr"/>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$13444万
+$48,500/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
+      <c r="G34" s="20" t="inlineStr"/>
+      <c r="H34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$13306万
+$48,000/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+$13055万
+$47,080/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr"/>
+      <c r="F35" s="20" t="inlineStr"/>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$13112万
+$47,300/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="inlineStr"/>
+      <c r="F36" s="20" t="inlineStr"/>
+      <c r="G36" s="20" t="inlineStr"/>
+      <c r="H36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr"/>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12940万
+$46,680/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+$12431万
+$44,830/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr"/>
+      <c r="F37" s="20" t="inlineStr"/>
+      <c r="G37" s="20" t="inlineStr"/>
+      <c r="H37" s="20" t="inlineStr"/>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12776万
+$46,090/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr"/>
+      <c r="F38" s="20" t="inlineStr"/>
+      <c r="G38" s="20" t="inlineStr"/>
+      <c r="H38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12837万
+$46,310/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="20" t="inlineStr"/>
+      <c r="G39" s="20" t="inlineStr"/>
+      <c r="H39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12751万
+$46,000/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr"/>
+      <c r="F40" s="20" t="inlineStr"/>
+      <c r="G40" s="20" t="inlineStr"/>
+      <c r="H40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
 招标单位
@@ -6093,63 +6257,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr"/>
-      <c r="F34" s="20" t="inlineStr"/>
-      <c r="G34" s="20" t="inlineStr"/>
-      <c r="H34" s="20" t="inlineStr"/>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr"/>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr"/>
-      <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="20" t="inlineStr"/>
-      <c r="H35" s="20" t="inlineStr"/>
-    </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="23" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D41" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
 -
@@ -6157,55 +6265,27 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr"/>
-      <c r="F36" s="20" t="inlineStr"/>
-      <c r="G36" s="20" t="inlineStr"/>
-      <c r="H36" s="20" t="inlineStr"/>
-    </row>
-    <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr"/>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="E41" s="20" t="inlineStr"/>
+      <c r="F41" s="20" t="inlineStr"/>
+      <c r="G41" s="20" t="inlineStr"/>
+      <c r="H41" s="20" t="inlineStr"/>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
-$12940万
-$46,680/呎
-(26年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="D37" s="22" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-$12431万
-$44,830/呎
-(26年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr"/>
-      <c r="F37" s="20" t="inlineStr"/>
-      <c r="G37" s="20" t="inlineStr"/>
-      <c r="H37" s="20" t="inlineStr"/>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr"/>
-      <c r="C38" s="23" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D42" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
 -
@@ -6213,118 +6293,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr"/>
-      <c r="F38" s="20" t="inlineStr"/>
-      <c r="G38" s="20" t="inlineStr"/>
-      <c r="H38" s="20" t="inlineStr"/>
-    </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="20" t="inlineStr"/>
-      <c r="F39" s="20" t="inlineStr"/>
-      <c r="G39" s="20" t="inlineStr"/>
-      <c r="H39" s="20" t="inlineStr"/>
-    </row>
-    <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr"/>
-      <c r="C40" s="23" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E40" s="20" t="inlineStr"/>
-      <c r="F40" s="20" t="inlineStr"/>
-      <c r="G40" s="20" t="inlineStr"/>
-      <c r="H40" s="20" t="inlineStr"/>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D41" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E41" s="20" t="inlineStr"/>
-      <c r="F41" s="20" t="inlineStr"/>
-      <c r="G41" s="20" t="inlineStr"/>
-      <c r="H41" s="20" t="inlineStr"/>
-    </row>
-    <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="inlineStr"/>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="E42" s="20" t="inlineStr"/>
       <c r="F42" s="20" t="inlineStr"/>
       <c r="G42" s="20" t="inlineStr"/>
@@ -6337,12 +6305,12 @@
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr"/>
-      <c r="C43" s="21" t="inlineStr">
+      <c r="C43" s="22" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
+$12696万
+$45,800/呎
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="D43" s="21" t="inlineStr">

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -1748,7 +1748,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -3591,23 +3591,19 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>130000000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>46881</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3616,12 +3612,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3631,7 +3627,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3855,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3869,12 +3865,12 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3884,12 +3880,12 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -3899,7 +3895,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4123,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4137,12 +4133,12 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -4152,12 +4148,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4167,7 +4163,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4605,23 +4601,19 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>128593080</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>46390</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4630,12 +4622,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4645,7 +4637,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5282,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5300,7 +5292,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5643,7 @@
           <t>- | 5483呎 (3房)
 $40869万
 $74,538/呎
-(26年-08月-19日)</t>
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
@@ -6061,7 +6053,63 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+$13000万
+$46,881/呎
+(26年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="inlineStr"/>
+      <c r="F34" s="20" t="inlineStr"/>
+      <c r="G34" s="20" t="inlineStr"/>
+      <c r="H34" s="20" t="inlineStr"/>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$13306万
+$48,000/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+$13055万
+$47,080/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr"/>
+      <c r="F35" s="20" t="inlineStr"/>
+      <c r="G35" s="20" t="inlineStr"/>
+      <c r="H35" s="20" t="inlineStr"/>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr"/>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$13112万
+$47,300/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
 招标单位
@@ -6069,55 +6117,83 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr"/>
-      <c r="F34" s="20" t="inlineStr"/>
-      <c r="G34" s="20" t="inlineStr"/>
-      <c r="H34" s="20" t="inlineStr"/>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr"/>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="E36" s="20" t="inlineStr"/>
+      <c r="F36" s="20" t="inlineStr"/>
+      <c r="G36" s="20" t="inlineStr"/>
+      <c r="H36" s="20" t="inlineStr"/>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr"/>
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
-$13306万
-$48,000/呎
+$12940万
+$46,680/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+$12431万
+$44,830/呎
+(26年-09月-10日)</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr"/>
+      <c r="F37" s="20" t="inlineStr"/>
+      <c r="G37" s="20" t="inlineStr"/>
+      <c r="H37" s="20" t="inlineStr"/>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12776万
+$46,090/呎
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
-$13055万
-$47,080/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr"/>
-      <c r="F35" s="20" t="inlineStr"/>
-      <c r="G35" s="20" t="inlineStr"/>
-      <c r="H35" s="20" t="inlineStr"/>
-    </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr"/>
-      <c r="C36" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="inlineStr"/>
+      <c r="F38" s="20" t="inlineStr"/>
+      <c r="G38" s="20" t="inlineStr"/>
+      <c r="H38" s="20" t="inlineStr"/>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
-$13112万
-$47,300/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
+$12837万
+$46,310/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
 -
@@ -6125,55 +6201,27 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr"/>
-      <c r="F36" s="20" t="inlineStr"/>
-      <c r="G36" s="20" t="inlineStr"/>
-      <c r="H36" s="20" t="inlineStr"/>
-    </row>
-    <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr"/>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="20" t="inlineStr"/>
+      <c r="G39" s="20" t="inlineStr"/>
+      <c r="H39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="22" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
-$12940万
-$46,680/呎
-(26年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="D37" s="22" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-$12431万
-$44,830/呎
-(26年-09月-10日)</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr"/>
-      <c r="F37" s="20" t="inlineStr"/>
-      <c r="G37" s="20" t="inlineStr"/>
-      <c r="H37" s="20" t="inlineStr"/>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr"/>
-      <c r="C38" s="22" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-$12776万
-$46,090/呎
+$12751万
+$46,000/呎
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="D38" s="21" t="inlineStr">
+      <c r="D40" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
 -
@@ -6181,62 +6229,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr"/>
-      <c r="F38" s="20" t="inlineStr"/>
-      <c r="G38" s="20" t="inlineStr"/>
-      <c r="H38" s="20" t="inlineStr"/>
-    </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="22" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-$12837万
-$46,310/呎
-(26年-09月-14日)</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E39" s="20" t="inlineStr"/>
-      <c r="F39" s="20" t="inlineStr"/>
-      <c r="G39" s="20" t="inlineStr"/>
-      <c r="H39" s="20" t="inlineStr"/>
-    </row>
-    <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr"/>
-      <c r="C40" s="22" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-$12751万
-$46,000/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="E40" s="20" t="inlineStr"/>
       <c r="F40" s="20" t="inlineStr"/>
       <c r="G40" s="20" t="inlineStr"/>
@@ -6249,12 +6241,12 @@
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
-招标单位
--
-(在售)</t>
+$12859万
+$46,390/呎
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -4817,12 +4817,12 @@
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -5093,12 +5093,12 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,147 @@
 (26年-09月-14日)</t>
         </is>
       </c>
-      <c r="D39" s="21" t="inlineStr">
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr"/>
+      <c r="F39" s="20" t="inlineStr"/>
+      <c r="G39" s="20" t="inlineStr"/>
+      <c r="H39" s="20" t="inlineStr"/>
+    </row>
+    <row r="40" ht="58" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12751万
+$46,000/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr"/>
+      <c r="F40" s="20" t="inlineStr"/>
+      <c r="G40" s="20" t="inlineStr"/>
+      <c r="H40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12859万
+$46,390/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr"/>
+      <c r="F41" s="20" t="inlineStr"/>
+      <c r="G41" s="20" t="inlineStr"/>
+      <c r="H41" s="20" t="inlineStr"/>
+    </row>
+    <row r="42" ht="58" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr"/>
+      <c r="F42" s="20" t="inlineStr"/>
+      <c r="G42" s="20" t="inlineStr"/>
+      <c r="H42" s="20" t="inlineStr"/>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr"/>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12696万
+$45,800/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr"/>
+      <c r="F43" s="20" t="inlineStr"/>
+      <c r="G43" s="20" t="inlineStr"/>
+      <c r="H43" s="20" t="inlineStr"/>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D44" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
 -
@@ -6201,146 +6341,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr"/>
-      <c r="F39" s="20" t="inlineStr"/>
-      <c r="G39" s="20" t="inlineStr"/>
-      <c r="H39" s="20" t="inlineStr"/>
-    </row>
-    <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B40" s="20" t="inlineStr"/>
-      <c r="C40" s="22" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-$12751万
-$46,000/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E40" s="20" t="inlineStr"/>
-      <c r="F40" s="20" t="inlineStr"/>
-      <c r="G40" s="20" t="inlineStr"/>
-      <c r="H40" s="20" t="inlineStr"/>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="22" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-$12859万
-$46,390/呎
-(26年-09月-15日)</t>
-        </is>
-      </c>
-      <c r="D41" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E41" s="20" t="inlineStr"/>
-      <c r="F41" s="20" t="inlineStr"/>
-      <c r="G41" s="20" t="inlineStr"/>
-      <c r="H41" s="20" t="inlineStr"/>
-    </row>
-    <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="inlineStr"/>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="inlineStr"/>
-      <c r="F42" s="20" t="inlineStr"/>
-      <c r="G42" s="20" t="inlineStr"/>
-      <c r="H42" s="20" t="inlineStr"/>
-    </row>
-    <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="inlineStr"/>
-      <c r="C43" s="22" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-$12696万
-$45,800/呎
-(26年-09月-14日)</t>
-        </is>
-      </c>
-      <c r="D43" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E43" s="20" t="inlineStr"/>
-      <c r="F43" s="20" t="inlineStr"/>
-      <c r="G43" s="20" t="inlineStr"/>
-      <c r="H43" s="20" t="inlineStr"/>
-    </row>
-    <row r="44" ht="58" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="inlineStr"/>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="E44" s="20" t="inlineStr"/>
       <c r="F44" s="20" t="inlineStr"/>
       <c r="G44" s="20" t="inlineStr"/>
@@ -6361,12 +6361,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D45" s="21" t="inlineStr">
+      <c r="D45" s="23" t="inlineStr">
         <is>
           <t>B | 2684呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -3855,23 +3855,19 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>131958000</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>47587</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3880,12 +3876,12 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -3895,7 +3891,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4123,23 +4119,19 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>124757000</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>44990</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4148,12 +4140,12 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4163,7 +4155,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4259,23 +4251,19 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>124174900</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>44780</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4284,12 +4272,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4299,7 +4287,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5260,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5282,7 +5270,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6109,12 +6097,12 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
-招标单位
--
-(在售)</t>
+$13196万
+$47,587/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr"/>
@@ -6165,12 +6153,12 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
-招标单位
--
-(在售)</t>
+$12476万
+$44,990/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr"/>
@@ -6193,12 +6181,12 @@
 (26年-09月-14日)</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
-招标单位
--
-(在售)</t>
+$12417万
+$44,780/呎
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2772</v>
+        <v>2716</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4058,14 +4058,14 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
         <v>129396960</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>46680</v>
+        <v>47642</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4383,23 +4383,19 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>123453960</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>44520</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4408,12 +4404,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4423,7 +4419,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4655,23 +4651,19 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>121734700</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>43900</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4680,12 +4672,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4695,7 +4687,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4795,23 +4787,19 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>121734700</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>43900</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4820,12 +4808,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4835,7 +4823,7 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5248,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5270,7 +5258,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6119,10 +6107,10 @@
       <c r="B37" s="20" t="inlineStr"/>
       <c r="C37" s="22" t="inlineStr">
         <is>
-          <t>A | 2772呎 (4+房)
+          <t>A | 2716呎 (4+房)
 $12940万
-$46,680/呎
-(26年-09月-10日)</t>
+$47,642/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -6209,7 +6197,35 @@
 (26年-09月-11日)</t>
         </is>
       </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>B | 2773呎 (4+房)
+$12345万
+$44,520/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="E40" s="20" t="inlineStr"/>
+      <c r="F40" s="20" t="inlineStr"/>
+      <c r="G40" s="20" t="inlineStr"/>
+      <c r="H40" s="20" t="inlineStr"/>
+    </row>
+    <row r="41" ht="58" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12859万
+$46,390/呎
+(26年-09月-15日)</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
 招标单位
@@ -6217,34 +6233,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr"/>
-      <c r="F40" s="20" t="inlineStr"/>
-      <c r="G40" s="20" t="inlineStr"/>
-      <c r="H40" s="20" t="inlineStr"/>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B41" s="20" t="inlineStr"/>
-      <c r="C41" s="22" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
-$12859万
-$46,390/呎
-(26年-09月-15日)</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
-        <is>
-          <t>B | 2773呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="E41" s="20" t="inlineStr"/>
       <c r="F41" s="20" t="inlineStr"/>
       <c r="G41" s="20" t="inlineStr"/>
@@ -6265,12 +6253,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D42" s="22" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
-招标单位
--
-(在售)</t>
+$12173万
+$43,900/呎
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr"/>
@@ -6293,12 +6281,12 @@
 (26年-09月-14日)</t>
         </is>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D43" s="22" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
-招标单位
--
-(在售)</t>
+$12173万
+$43,900/呎
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3728,14 +3728,14 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
         <v>130552000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>47080</v>
+        <v>47944</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2772</v>
+        <v>2716</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
         <v>131115600</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>47300</v>
+        <v>48275</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2772</v>
+        <v>2716</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>127761000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>46090</v>
+        <v>47040</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2772</v>
+        <v>2716</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>128371000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>46310</v>
+        <v>47265</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4515,23 +4515,19 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>122789000</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>44280</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4540,12 +4536,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4555,7 +4551,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5244,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5258,7 +5254,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6059,10 +6055,10 @@
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $13055万
-$47,080/呎
-(26年-09月-11日)</t>
+$47,944/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr"/>
@@ -6079,10 +6075,10 @@
       <c r="B36" s="20" t="inlineStr"/>
       <c r="C36" s="22" t="inlineStr">
         <is>
-          <t>A | 2772呎 (4+房)
+          <t>A | 2716呎 (4+房)
 $13112万
-$47,300/呎
-(26年-09月-11日)</t>
+$48,275/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -6135,9 +6131,9 @@
       <c r="B38" s="20" t="inlineStr"/>
       <c r="C38" s="22" t="inlineStr">
         <is>
-          <t>A | 2772呎 (4+房)
+          <t>A | 2716呎 (4+房)
 $12776万
-$46,090/呎
+$47,040/呎
 (26年-09月-11日)</t>
         </is>
       </c>
@@ -6163,9 +6159,9 @@
       <c r="B39" s="20" t="inlineStr"/>
       <c r="C39" s="22" t="inlineStr">
         <is>
-          <t>A | 2772呎 (4+房)
+          <t>A | 2716呎 (4+房)
 $12837万
-$46,310/呎
+$47,265/呎
 (26年-09月-14日)</t>
         </is>
       </c>
@@ -6225,12 +6221,12 @@
 (26年-09月-15日)</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
-招标单位
--
-(在售)</t>
+$12279万
+$44,280/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2772</v>
+        <v>2716</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3794,14 +3794,14 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
         <v>133056000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>48000</v>
+        <v>48990</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>131958000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>47587</v>
+        <v>48461</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>124757000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>44990</v>
+        <v>45816</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>124174900</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>44780</v>
+        <v>45602</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2772</v>
+        <v>2716</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4454,14 +4454,14 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
         <v>127512000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>46000</v>
+        <v>46948</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2772</v>
+        <v>2716</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4854,14 +4854,14 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
         <v>126957600</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>45800</v>
+        <v>46744</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -6047,10 +6047,10 @@
       <c r="B35" s="20" t="inlineStr"/>
       <c r="C35" s="22" t="inlineStr">
         <is>
-          <t>A | 2772呎 (4+房)
+          <t>A | 2716呎 (4+房)
 $13306万
-$48,000/呎
-(26年-09月-11日)</t>
+$48,990/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -6083,9 +6083,9 @@
       </c>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $13196万
-$47,587/呎
+$48,461/呎
 (26年-09月-24日)</t>
         </is>
       </c>
@@ -6134,14 +6134,14 @@
           <t>A | 2716呎 (4+房)
 $12776万
 $47,040/呎
-(26年-09月-11日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $12476万
-$44,990/呎
+$45,816/呎
 (26年-09月-22日)</t>
         </is>
       </c>
@@ -6162,14 +6162,14 @@
           <t>A | 2716呎 (4+房)
 $12837万
 $47,265/呎
-(26年-09月-14日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $12417万
-$44,780/呎
+$45,602/呎
 (26年-09月-23日)</t>
         </is>
       </c>
@@ -6187,10 +6187,10 @@
       <c r="B40" s="20" t="inlineStr"/>
       <c r="C40" s="22" t="inlineStr">
         <is>
-          <t>A | 2772呎 (4+房)
+          <t>A | 2716呎 (4+房)
 $12751万
-$46,000/呎
-(26年-09月-11日)</t>
+$46,948/呎
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -6271,10 +6271,10 @@
       <c r="B43" s="20" t="inlineStr"/>
       <c r="C43" s="22" t="inlineStr">
         <is>
-          <t>A | 2772呎 (4+房)
+          <t>A | 2716呎 (4+房)
 $12696万
-$45,800/呎
-(26年-09月-14日)</t>
+$46,744/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="D43" s="22" t="inlineStr">

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2772</v>
+        <v>2716</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3662,14 +3662,14 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
         <v>134442000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>48500</v>
+        <v>49500</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3992,14 +3992,14 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
         <v>124313590</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>44830</v>
+        <v>45653</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2772</v>
+        <v>2716</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4586,14 +4586,14 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
         <v>128593080</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>46390</v>
+        <v>47346</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -6019,10 +6019,10 @@
       <c r="B34" s="20" t="inlineStr"/>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>A | 2772呎 (4+房)
+          <t>A | 2716呎 (4+房)
 $13444万
-$48,500/呎
-(26年-09月-11日)</t>
+$49,500/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -6111,10 +6111,10 @@
       </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $12431万
-$44,830/呎
-(26年-09月-10日)</t>
+$45,653/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr"/>
@@ -6215,10 +6215,10 @@
       <c r="B41" s="20" t="inlineStr"/>
       <c r="C41" s="22" t="inlineStr">
         <is>
-          <t>A | 2772呎 (4+房)
+          <t>A | 2716呎 (4+房)
 $12859万
-$46,390/呎
-(26年-09月-15日)</t>
+$47,346/呎
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -4256,7 +4256,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4652,14 +4652,14 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
         <v>121734700</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>43900</v>
+        <v>44706</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4788,14 +4788,14 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
         <v>121734700</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>43900</v>
+        <v>44706</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
           <t>B | 2723呎 (4+房)
 $12417万
 $45,602/呎
-(26年-09月-23日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr"/>
@@ -6241,20 +6241,20 @@
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr"/>
-      <c r="C42" s="21" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D42" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $12173万
-$43,900/呎
-(26年-09月-25日)</t>
+$44,706/呎
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr"/>
@@ -6279,10 +6279,10 @@
       </c>
       <c r="D43" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $12173万
-$43,900/呎
-(26年-09月-25日)</t>
+$44,706/呎
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3596,14 +3596,14 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
         <v>130000000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>46881</v>
+        <v>47741</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4388,14 +4388,14 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
         <v>123453960</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>44520</v>
+        <v>45337</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2773</v>
+        <v>2723</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4520,14 +4520,14 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
         <v>122789000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>44280</v>
+        <v>45093</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4713,23 +4713,19 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>128280000</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>46277</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4738,12 +4734,12 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -4753,7 +4749,7 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4981,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -4995,12 +4991,12 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -5010,12 +5006,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -5025,7 +5021,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5055,23 +5051,19 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>149124000</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>55560</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5080,12 +5072,12 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -5095,7 +5087,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5236,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5254,7 +5246,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5264,7 +5256,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -6027,10 +6019,10 @@
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $13000万
-$46,881/呎
-(26年-09月-16日)</t>
+$47,741/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr"/>
@@ -6086,7 +6078,7 @@
           <t>B | 2723呎 (4+房)
 $13196万
 $48,461/呎
-(26年-09月-24日)</t>
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr"/>
@@ -6142,7 +6134,7 @@
           <t>B | 2723呎 (4+房)
 $12476万
 $45,816/呎
-(26年-09月-22日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr"/>
@@ -6195,10 +6187,10 @@
       </c>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $12345万
-$44,520/呎
-(26年-09月-28日)</t>
+$45,337/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr"/>
@@ -6223,10 +6215,10 @@
       </c>
       <c r="D41" s="22" t="inlineStr">
         <is>
-          <t>B | 2773呎 (4+房)
+          <t>B | 2723呎 (4+房)
 $12279万
-$44,280/呎
-(26年-09月-29日)</t>
+$45,093/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr"/>
@@ -6241,7 +6233,63 @@
         </is>
       </c>
       <c r="B42" s="20" t="inlineStr"/>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>A | 2772呎 (4+房)
+$12828万
+$46,277/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$12173万
+$44,706/呎
+(26年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr"/>
+      <c r="F42" s="20" t="inlineStr"/>
+      <c r="G42" s="20" t="inlineStr"/>
+      <c r="H42" s="20" t="inlineStr"/>
+    </row>
+    <row r="43" ht="58" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr"/>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>A | 2716呎 (4+房)
+$12696万
+$46,744/呎
+(26年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>B | 2723呎 (4+房)
+$12173万
+$44,706/呎
+(26年-10月-15日)</t>
+        </is>
+      </c>
+      <c r="E43" s="20" t="inlineStr"/>
+      <c r="F43" s="20" t="inlineStr"/>
+      <c r="G43" s="20" t="inlineStr"/>
+      <c r="H43" s="20" t="inlineStr"/>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr"/>
+      <c r="C44" s="23" t="inlineStr">
         <is>
           <t>A | 2772呎 (4+房)
 招标单位
@@ -6249,62 +6297,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$12173万
-$44,706/呎
-(26年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="inlineStr"/>
-      <c r="F42" s="20" t="inlineStr"/>
-      <c r="G42" s="20" t="inlineStr"/>
-      <c r="H42" s="20" t="inlineStr"/>
-    </row>
-    <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B43" s="20" t="inlineStr"/>
-      <c r="C43" s="22" t="inlineStr">
-        <is>
-          <t>A | 2716呎 (4+房)
-$12696万
-$46,744/呎
-(26年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="inlineStr">
-        <is>
-          <t>B | 2723呎 (4+房)
-$12173万
-$44,706/呎
-(26年-10月-15日)</t>
-        </is>
-      </c>
-      <c r="E43" s="20" t="inlineStr"/>
-      <c r="F43" s="20" t="inlineStr"/>
-      <c r="G43" s="20" t="inlineStr"/>
-      <c r="H43" s="20" t="inlineStr"/>
-    </row>
-    <row r="44" ht="58" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B44" s="20" t="inlineStr"/>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>A | 2772呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D44" s="21" t="inlineStr">
         <is>
           <t>B | 2773呎 (4+房)
@@ -6333,12 +6325,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D45" s="22" t="inlineStr">
         <is>
           <t>B | 2684呎 (4+房)
-招标单位
--
-(在售)</t>
+$14912万
+$55,560/呎
+(26年-10月-16日)</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr"/>

--- a/web/files/港岛-半山区西部-天御第2期.xlsx
+++ b/web/files/港岛-半山区西部-天御第2期.xlsx
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5470</v>
+        <v>5577</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>422912000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>77315</v>
+        <v>75831</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5483</v>
+        <v>5590</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>408690000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>74538</v>
+        <v>73111</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5483</v>
+        <v>5590</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>373610000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>68140</v>
+        <v>66835</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>157783000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>57945</v>
+        <v>56900</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2727</v>
+        <v>2782</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>161333000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>59161</v>
+        <v>57992</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>164688000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>60480</v>
+        <v>59390</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2727</v>
+        <v>2782</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>155800000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>57132</v>
+        <v>56003</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2727</v>
+        <v>2782</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>158087000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>57971</v>
+        <v>56825</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>147781000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>54271</v>
+        <v>53293</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2727</v>
+        <v>2782</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>154100000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>56509</v>
+        <v>55392</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>151937000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>55798</v>
+        <v>54792</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2727</v>
+        <v>2782</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>150714000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>55267</v>
+        <v>54175</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>144150000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>52938</v>
+        <v>51983</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>149339000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>54985</v>
+        <v>53874</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>141380000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>51921</v>
+        <v>50984</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>136936800</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>50419</v>
+        <v>49400</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>133935900</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>49187</v>
+        <v>48300</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>135828000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>50010</v>
+        <v>49000</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135831000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>49883</v>
+        <v>48983</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>141545360</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>52115</v>
+        <v>51063</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>136380000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>50084</v>
+        <v>49181</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>141500000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>52099</v>
+        <v>51046</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>131829000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>48413</v>
+        <v>47540</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>132717000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>48865</v>
+        <v>47878</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>141621970</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>52010</v>
+        <v>51072</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>129729600</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>47765</v>
+        <v>46800</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>128588000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>47223</v>
+        <v>46371</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>129231000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>47581</v>
+        <v>46620</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>130000000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>47741</v>
+        <v>46881</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>134442000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>49500</v>
+        <v>48500</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>130552000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>47944</v>
+        <v>47080</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>133056000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>48990</v>
+        <v>48000</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>131958000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>48461</v>
+        <v>47587</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>131115600</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>48275</v>
+        <v>47300</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3983,7 +3983,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>124313590</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>45653</v>
+        <v>44830</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>129396960</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>47642</v>
+        <v>46680</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>124757000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>45816</v>
+        <v>44990</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>127761000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>47040</v>
+        <v>46090</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>124174900</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>45602</v>
+        <v>44780</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>128371000</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>47265</v>
+        <v>46310</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>123453960</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>45337</v>
+        <v>44520</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>127512000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>46948</v>
+        <v>46000</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>122789000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>45093</v>
+        <v>44280</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>128593080</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>47346</v>
+        <v>46390</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4659,7 +4659,7 @@
         <v>121734700</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>44706</v>
+        <v>43900</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>2723</v>
+        <v>2773</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>121734700</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>44706</v>
+        <v>43900</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2716</v>
+        <v>2772</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>126957600</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>46744</v>
+        <v>45800</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -5562,9 +5562,9 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>- | 5470呎 (4+房)
+          <t>- | 5577呎 (4+房)
 $42291万
-$77,315/呎
+$75,831/呎
 (26年-02月-05日)</t>
         </is>
       </c>
@@ -5604,9 +5604,9 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>- | 5483呎 (3房)
+          <t>- | 5590呎 (3房)
 $40869万
-$74,538/呎
+$73,111/呎
 (26年-09月-14日)</t>
         </is>
       </c>
@@ -5625,9 +5625,9 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>- | 5483呎 (3房)
+          <t>- | 5590呎 (3房)
 $37361万
-$68,140/呎
+$66,835/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -5647,17 +5647,17 @@
       <c r="B21" s="20" t="inlineStr"/>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>A | 2727呎 (4+房)
+          <t>A | 2782呎 (4+房)
 $16133万
-$59,161/呎
+$57,992/呎
 (25年-11月-18日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $15778万
-$57,945/呎
+$56,900/呎
 (25年-11月-18日)</t>
         </is>
       </c>
@@ -5675,17 +5675,17 @@
       <c r="B22" s="20" t="inlineStr"/>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>A | 2727呎 (4+房)
+          <t>A | 2782呎 (4+房)
 $15580万
-$57,132/呎
+$56,003/呎
 (26年-02月-11日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $16469万
-$60,480/呎
+$59,390/呎
 (26年-03月-31日)</t>
         </is>
       </c>
@@ -5703,9 +5703,9 @@
       <c r="B23" s="20" t="inlineStr"/>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>A | 2727呎 (4+房)
+          <t>A | 2782呎 (4+房)
 $15809万
-$57,971/呎
+$56,825/呎
 (26年-02月-11日)</t>
         </is>
       </c>
@@ -5731,17 +5731,17 @@
       <c r="B24" s="20" t="inlineStr"/>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>A | 2727呎 (4+房)
+          <t>A | 2782呎 (4+房)
 $15410万
-$56,509/呎
+$55,392/呎
 (26年-02月-06日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $14778万
-$54,271/呎
+$53,293/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -5759,17 +5759,17 @@
       <c r="B25" s="20" t="inlineStr"/>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>A | 2727呎 (4+房)
+          <t>A | 2782呎 (4+房)
 $15071万
-$55,267/呎
+$54,175/呎
 (26年-03月-03日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $15194万
-$55,798/呎
+$54,792/呎
 (25年-12月-11日)</t>
         </is>
       </c>
@@ -5787,17 +5787,17 @@
       <c r="B26" s="20" t="inlineStr"/>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $14934万
-$54,985/呎
+$53,874/呎
 (25年-12月-04日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $14415万
-$52,938/呎
+$51,983/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -5815,17 +5815,17 @@
       <c r="B27" s="20" t="inlineStr"/>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $13694万
-$50,419/呎
+$49,400/呎
 (25年-12月-16日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $14138万
-$51,921/呎
+$50,984/呎
 (26年-01月-28日)</t>
         </is>
       </c>
@@ -5843,17 +5843,17 @@
       <c r="B28" s="20" t="inlineStr"/>
       <c r="C28" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $13583万
-$50,010/呎
+$49,000/呎
 (26年-01月-29日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $13394万
-$49,187/呎
+$48,300/呎
 (25年-12月-12日)</t>
         </is>
       </c>
@@ -5871,17 +5871,17 @@
       <c r="B29" s="20" t="inlineStr"/>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $14155万
-$52,115/呎
+$51,063/呎
 (26年-02月-09日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $13583万
-$49,883/呎
+$48,983/呎
 (25年-12月-16日)</t>
         </is>
       </c>
@@ -5899,17 +5899,17 @@
       <c r="B30" s="20" t="inlineStr"/>
       <c r="C30" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $14150万
-$52,099/呎
+$51,046/呎
 (26年-03月-16日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $13638万
-$50,084/呎
+$49,181/呎
 (26年-02月-12日)</t>
         </is>
       </c>
@@ -5927,17 +5927,17 @@
       <c r="B31" s="20" t="inlineStr"/>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $13272万
-$48,865/呎
+$47,878/呎
 (26年-02月-12日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $13183万
-$48,413/呎
+$47,540/呎
 (26年-02月-12日)</t>
         </is>
       </c>
@@ -5955,17 +5955,17 @@
       <c r="B32" s="20" t="inlineStr"/>
       <c r="C32" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $12973万
-$47,765/呎
+$46,800/呎
 (26年-03月-04日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $14162万
-$52,010/呎
+$51,072/呎
 (26年-04月-14日)</t>
         </is>
       </c>
@@ -5983,17 +5983,17 @@
       <c r="B33" s="20" t="inlineStr"/>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $12923万
-$47,581/呎
+$46,620/呎
 (26年-03月-27日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $12859万
-$47,223/呎
+$46,371/呎
 (26年-01月-15日)</t>
         </is>
       </c>
@@ -6011,17 +6011,17 @@
       <c r="B34" s="20" t="inlineStr"/>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $13444万
-$49,500/呎
+$48,500/呎
 (26年-10月-13日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $13000万
-$47,741/呎
+$46,881/呎
 (26年-10月-16日)</t>
         </is>
       </c>
@@ -6039,17 +6039,17 @@
       <c r="B35" s="20" t="inlineStr"/>
       <c r="C35" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $13306万
-$48,990/呎
+$48,000/呎
 (26年-10月-06日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $13055万
-$47,944/呎
+$47,080/呎
 (26年-09月-29日)</t>
         </is>
       </c>
@@ -6067,17 +6067,17 @@
       <c r="B36" s="20" t="inlineStr"/>
       <c r="C36" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $13112万
-$48,275/呎
+$47,300/呎
 (26年-09月-30日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $13196万
-$48,461/呎
+$47,587/呎
 (26年-10月-22日)</t>
         </is>
       </c>
@@ -6095,17 +6095,17 @@
       <c r="B37" s="20" t="inlineStr"/>
       <c r="C37" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $12940万
-$47,642/呎
+$46,680/呎
 (26年-09月-28日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $12431万
-$45,653/呎
+$44,830/呎
 (26年-10月-09日)</t>
         </is>
       </c>
@@ -6123,17 +6123,17 @@
       <c r="B38" s="20" t="inlineStr"/>
       <c r="C38" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $12776万
-$47,040/呎
+$46,090/呎
 (26年-10月-05日)</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $12476万
-$45,816/呎
+$44,990/呎
 (26年-10月-20日)</t>
         </is>
       </c>
@@ -6151,17 +6151,17 @@
       <c r="B39" s="20" t="inlineStr"/>
       <c r="C39" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $12837万
-$47,265/呎
+$46,310/呎
 (26年-10月-05日)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $12417万
-$45,602/呎
+$44,780/呎
 (26年-10月-15日)</t>
         </is>
       </c>
@@ -6179,17 +6179,17 @@
       <c r="B40" s="20" t="inlineStr"/>
       <c r="C40" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $12751万
-$46,948/呎
+$46,000/呎
 (26年-10月-07日)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $12345万
-$45,337/呎
+$44,520/呎
 (26年-10月-27日)</t>
         </is>
       </c>
@@ -6207,17 +6207,17 @@
       <c r="B41" s="20" t="inlineStr"/>
       <c r="C41" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $12859万
-$47,346/呎
+$46,390/呎
 (26年-10月-09日)</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $12279万
-$45,093/呎
+$44,280/呎
 (26年-10月-26日)</t>
         </is>
       </c>
@@ -6243,9 +6243,9 @@
       </c>
       <c r="D42" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $12173万
-$44,706/呎
+$43,900/呎
 (26年-10月-15日)</t>
         </is>
       </c>
@@ -6263,17 +6263,17 @@
       <c r="B43" s="20" t="inlineStr"/>
       <c r="C43" s="22" t="inlineStr">
         <is>
-          <t>A | 2716呎 (4+房)
+          <t>A | 2772呎 (4+房)
 $12696万
-$46,744/呎
+$45,800/呎
 (26年-10月-06日)</t>
         </is>
       </c>
       <c r="D43" s="22" t="inlineStr">
         <is>
-          <t>B | 2723呎 (4+房)
+          <t>B | 2773呎 (4+房)
 $12173万
-$44,706/呎
+$43,900/呎
 (26年-10月-15日)</t>
         </is>
       </c>
